--- a/data/trans_dic/P14B23-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P14B23-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas discapacitantes de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población cuya depresión o ansiedad le limita (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,3</t>
+          <t>0,44; 2,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,22</t>
+          <t>0,23; 2,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,09</t>
+          <t>1,05; 3,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 5,35</t>
+          <t>0,59; 5,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 5,45</t>
+          <t>1,43; 5,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 7,18</t>
+          <t>3,52; 7,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,26</t>
+          <t>0,78; 3,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,04</t>
+          <t>1,03; 3,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,78</t>
+          <t>2,52; 4,65</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,1</t>
+          <t>0,95; 4,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,92</t>
+          <t>0,49; 3,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,37</t>
+          <t>1,48; 4,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,75</t>
+          <t>1,68; 5,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,96</t>
+          <t>1,02; 4,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,94; 9,33</t>
+          <t>4,97; 9,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,03</t>
+          <t>1,58; 4,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,96</t>
+          <t>1,04; 3,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,48; 6,15</t>
+          <t>3,45; 5,98</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,89; 6,43</t>
+          <t>2,91; 6,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,8</t>
+          <t>0,54; 2,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 6,04</t>
+          <t>1,07; 6,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,45; 12,51</t>
+          <t>5,65; 12,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 14,45</t>
+          <t>5,17; 14,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,96; 14,36</t>
+          <t>7,22; 14,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,03; 7,21</t>
+          <t>4,17; 7,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,98</t>
+          <t>2,07; 5,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 7,48</t>
+          <t>2,03; 7,23</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,17</t>
+          <t>2,02; 3,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,79</t>
+          <t>1,79; 3,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 5,83</t>
+          <t>3,16; 5,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,01; 9,02</t>
+          <t>5,14; 8,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,53; 6,76</t>
+          <t>3,53; 6,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 8,09</t>
+          <t>3,19; 8,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,64; 5,58</t>
+          <t>3,57; 5,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 4,54</t>
+          <t>2,81; 4,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,14</t>
+          <t>3,48; 6,16</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,09</t>
+          <t>0,78; 3,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,66</t>
+          <t>1,92; 4,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,15; 6,91</t>
+          <t>3,09; 7,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,91; 13,63</t>
+          <t>9,12; 13,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,68; 12,11</t>
+          <t>7,42; 12,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,64; 10,97</t>
+          <t>6,8; 11,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,04; 9,04</t>
+          <t>6,12; 9,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,37; 8,21</t>
+          <t>5,45; 8,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,05; 8,99</t>
+          <t>5,96; 9,1</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,85; 10,23</t>
+          <t>1,94; 10,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,99; 11,75</t>
+          <t>7,96; 11,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,78; 10,31</t>
+          <t>6,75; 10,17</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,56; 10,17</t>
+          <t>6,46; 9,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,48; 9,22</t>
+          <t>6,33; 9,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,53; 8,34</t>
+          <t>5,41; 8,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,8; 8,74</t>
+          <t>5,74; 9,11</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,91; 3,02</t>
+          <t>1,91; 3,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,54</t>
+          <t>1,51; 2,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 4,45</t>
+          <t>2,79; 4,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,06; 9,02</t>
+          <t>7,13; 8,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,83; 7,64</t>
+          <t>5,9; 7,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,9; 8,15</t>
+          <t>5,99; 8,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,75; 5,87</t>
+          <t>4,77; 5,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,9; 4,91</t>
+          <t>3,89; 4,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,71; 6,13</t>
+          <t>4,74; 6,13</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas discapacitantes de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población cuya depresión o ansiedad le limita (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2000; 14415</t>
+          <t>1926; 12978</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1007; 9547</t>
+          <t>1006; 9026</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5268; 20682</t>
+          <t>5290; 19148</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2561; 16813</t>
+          <t>1866; 15815</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4644; 18928</t>
+          <t>4956; 18424</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15729; 32137</t>
+          <t>15764; 32261</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6427; 24503</t>
+          <t>5855; 23684</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7864; 23556</t>
+          <t>8016; 23972</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>24083; 45542</t>
+          <t>23966; 44262</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3047; 17158</t>
+          <t>3958; 17601</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1838; 11026</t>
+          <t>1851; 11882</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6560; 19755</t>
+          <t>6709; 20087</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5060; 19447</t>
+          <t>5670; 20080</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4112; 18458</t>
+          <t>3783; 16655</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18883; 35676</t>
+          <t>19023; 35826</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11164; 30467</t>
+          <t>11952; 30451</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7490; 22170</t>
+          <t>7798; 22464</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29034; 51380</t>
+          <t>28821; 49924</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18156; 40386</t>
+          <t>18284; 41940</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2908; 14618</t>
+          <t>2810; 14358</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6816; 40357</t>
+          <t>7119; 41609</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14125; 32410</t>
+          <t>14634; 32904</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8604; 24011</t>
+          <t>8592; 24433</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11621; 23970</t>
+          <t>12050; 23696</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35747; 63944</t>
+          <t>37047; 65268</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14200; 34263</t>
+          <t>14208; 35274</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15364; 62481</t>
+          <t>16961; 60373</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22830; 48252</t>
+          <t>23350; 46128</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20476; 43554</t>
+          <t>20573; 43077</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34142; 60380</t>
+          <t>32723; 59078</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38028; 68445</t>
+          <t>38980; 67440</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29140; 55805</t>
+          <t>29158; 54668</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27978; 79165</t>
+          <t>31177; 79529</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>69782; 106910</t>
+          <t>68501; 105376</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>55352; 89628</t>
+          <t>55539; 90353</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>74929; 123537</t>
+          <t>70031; 123909</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3956; 15768</t>
+          <t>3983; 15960</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11522; 28905</t>
+          <t>11900; 29264</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14974; 32827</t>
+          <t>14682; 33542</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>67669; 103501</t>
+          <t>69260; 103729</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>56698; 89375</t>
+          <t>54750; 90089</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55823; 92324</t>
+          <t>57175; 93809</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>76759; 114758</t>
+          <t>77717; 116254</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>72937; 111580</t>
+          <t>74125; 111760</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>79661; 118280</t>
+          <t>78428; 119745</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1926</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5616</t>
+          <t>0; 4788</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4439; 24599</t>
+          <t>4660; 24689</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>88598; 130311</t>
+          <t>88309; 129446</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>73400; 111512</t>
+          <t>72987; 110072</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>49931; 77458</t>
+          <t>49217; 75946</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>89129; 126906</t>
+          <t>87132; 126729</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>75764; 114174</t>
+          <t>74098; 112033</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>58105; 87526</t>
+          <t>57523; 91289</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>65449; 103381</t>
+          <t>65191; 105020</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>51705; 86095</t>
+          <t>51052; 83777</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>91873; 150067</t>
+          <t>94247; 148869</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>249840; 319036</t>
+          <t>252255; 317264</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>205800; 269968</t>
+          <t>208471; 269509</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>211026; 291492</t>
+          <t>214278; 294195</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>330664; 408253</t>
+          <t>332013; 407616</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>269837; 339632</t>
+          <t>269109; 342580</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>327582; 426011</t>
+          <t>329709; 426236</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P14B23-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P14B23-Clase-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,97</t>
+          <t>0,45; 3,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,1</t>
+          <t>0,23; 2,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,79</t>
+          <t>1,0; 3,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,03</t>
+          <t>0,6; 5,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,31</t>
+          <t>1,39; 5,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 7,21</t>
+          <t>3,81; 7,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,15</t>
+          <t>0,86; 3,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,09</t>
+          <t>1,01; 2,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 4,65</t>
+          <t>2,48; 4,77</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,2</t>
+          <t>0,74; 3,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 3,15</t>
+          <t>0,49; 2,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,44</t>
+          <t>1,3; 4,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,94</t>
+          <t>1,51; 5,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,47</t>
+          <t>1,01; 4,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,97; 9,36</t>
+          <t>5,14; 9,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,02</t>
+          <t>1,56; 4,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,0</t>
+          <t>1,04; 3,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 5,98</t>
+          <t>3,43; 5,96</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 6,67</t>
+          <t>2,8; 6,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,75</t>
+          <t>0,55; 2,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 6,23</t>
+          <t>3,15; 7,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,65; 12,7</t>
+          <t>5,52; 12,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,17; 14,71</t>
+          <t>5,37; 15,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,22; 14,2</t>
+          <t>6,96; 14,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,17; 7,35</t>
+          <t>4,16; 7,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,13</t>
+          <t>2,09; 5,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 7,23</t>
+          <t>4,78; 8,4</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 3,98</t>
+          <t>1,96; 4,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,75</t>
+          <t>1,78; 3,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,16; 5,71</t>
+          <t>3,39; 5,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,14; 8,89</t>
+          <t>5,08; 8,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,53; 6,62</t>
+          <t>3,71; 6,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 8,13</t>
+          <t>6,25; 9,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 5,5</t>
+          <t>3,57; 5,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,57</t>
+          <t>2,83; 4,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,48; 6,16</t>
+          <t>4,92; 6,86</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,13</t>
+          <t>0,78; 3,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,71</t>
+          <t>1,95; 4,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,09; 7,06</t>
+          <t>2,77; 6,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,12; 13,66</t>
+          <t>9,17; 13,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,42; 12,2</t>
+          <t>7,52; 12,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,8; 11,15</t>
+          <t>8,59; 11,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,12; 9,16</t>
+          <t>6,04; 8,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,45; 8,22</t>
+          <t>5,33; 8,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,96; 9,1</t>
+          <t>6,7; 9,14</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -1233,42 +1233,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,94; 10,27</t>
+          <t>1,9; 9,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,96; 11,67</t>
+          <t>8,12; 11,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,75; 10,17</t>
+          <t>6,88; 10,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,46; 9,97</t>
+          <t>6,53; 9,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,33; 9,21</t>
+          <t>6,44; 9,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,41; 8,18</t>
+          <t>5,47; 8,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,74; 9,11</t>
+          <t>5,79; 9,05</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,91; 3,07</t>
+          <t>1,93; 3,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,47</t>
+          <t>1,54; 2,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,79; 4,41</t>
+          <t>3,18; 4,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,13; 8,97</t>
+          <t>7,23; 9,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,9; 7,63</t>
+          <t>5,79; 7,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,99; 8,22</t>
+          <t>7,34; 8,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,77; 5,86</t>
+          <t>4,82; 5,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,89; 4,95</t>
+          <t>3,94; 4,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,74; 6,13</t>
+          <t>5,49; 6,49</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10334</t>
+          <t>10890</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22849</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33182</t>
+          <t>36752</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1926; 12978</t>
+          <t>1987; 15469</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1006; 9026</t>
+          <t>997; 9087</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5290; 19148</t>
+          <t>5495; 19849</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1866; 15815</t>
+          <t>1900; 15950</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4956; 18424</t>
+          <t>4819; 18621</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15764; 32261</t>
+          <t>18599; 36217</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5855; 23684</t>
+          <t>6477; 23393</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8016; 23972</t>
+          <t>7850; 23132</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23966; 44262</t>
+          <t>25774; 49566</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11709</t>
+          <t>12146</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26555</t>
+          <t>29674</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>38264</t>
+          <t>41821</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3958; 17601</t>
+          <t>3086; 16351</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1851; 11882</t>
+          <t>1839; 10611</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6709; 20087</t>
+          <t>6296; 20171</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5670; 20080</t>
+          <t>5112; 18999</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3783; 16655</t>
+          <t>3755; 15790</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19023; 35826</t>
+          <t>21745; 39199</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11952; 30451</t>
+          <t>11799; 31393</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7798; 22464</t>
+          <t>7765; 24079</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28821; 49924</t>
+          <t>31111; 54019</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22697</t>
+          <t>23260</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16994</t>
+          <t>19267</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39691</t>
+          <t>42527</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18284; 41940</t>
+          <t>17605; 39310</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2810; 14358</t>
+          <t>2851; 14196</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7119; 41609</t>
+          <t>14835; 33850</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14634; 32904</t>
+          <t>14291; 32935</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8592; 24433</t>
+          <t>8924; 26010</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12050; 23696</t>
+          <t>13050; 27007</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37047; 65268</t>
+          <t>36949; 64401</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14208; 35274</t>
+          <t>14392; 34503</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16961; 60373</t>
+          <t>31492; 55378</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44719</t>
+          <t>50288</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57435</t>
+          <t>65755</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>102154</t>
+          <t>116043</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23350; 46128</t>
+          <t>22735; 48773</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20573; 43077</t>
+          <t>20485; 43111</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32723; 59078</t>
+          <t>38347; 64923</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38980; 67440</t>
+          <t>38549; 67055</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29158; 54668</t>
+          <t>30638; 55735</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31177; 79529</t>
+          <t>53818; 80149</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>68501; 105376</t>
+          <t>68408; 105732</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>55539; 90353</t>
+          <t>56005; 91363</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>70031; 123909</t>
+          <t>98025; 136789</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22686</t>
+          <t>24445</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76516</t>
+          <t>84651</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>99202</t>
+          <t>109096</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3983; 15960</t>
+          <t>3992; 16337</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11900; 29264</t>
+          <t>12093; 29428</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14682; 33542</t>
+          <t>15759; 35528</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>69260; 103729</t>
+          <t>69652; 103534</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>54750; 90089</t>
+          <t>55527; 89366</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>57175; 93809</t>
+          <t>71394; 98463</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>77717; 116254</t>
+          <t>76743; 113673</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>74125; 111760</t>
+          <t>72375; 110830</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>78428; 119745</t>
+          <t>93669; 127807</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10685</t>
+          <t>10606</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61305</t>
+          <t>66996</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>71990</t>
+          <t>77602</t>
         </is>
       </c>
     </row>
@@ -2459,42 +2459,42 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4788</t>
+          <t>0; 4045</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4660; 24689</t>
+          <t>4516; 23523</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>88309; 129446</t>
+          <t>90119; 130813</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>72987; 110072</t>
+          <t>74463; 110849</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>49217; 75946</t>
+          <t>55164; 82949</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>87132; 126729</t>
+          <t>88582; 126384</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>74098; 112033</t>
+          <t>74833; 112852</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>57523; 91289</t>
+          <t>62581; 97825</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>122829</t>
+          <t>131635</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>261653</t>
+          <t>292206</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>384482</t>
+          <t>423841</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>65191; 105020</t>
+          <t>66091; 103406</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>51052; 83777</t>
+          <t>52196; 84204</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>94247; 148869</t>
+          <t>109553; 157414</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>252255; 317264</t>
+          <t>255810; 320709</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>208471; 269509</t>
+          <t>204552; 267901</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>214278; 294195</t>
+          <t>266719; 323507</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>332013; 407616</t>
+          <t>335673; 409515</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>269109; 342580</t>
+          <t>272231; 343325</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>329709; 426236</t>
+          <t>388502; 459234</t>
         </is>
       </c>
     </row>
